--- a/MiniTemplate/Datas/random.xlsx
+++ b/MiniTemplate/Datas/random.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity Project\TimeChip\TimeChip\MiniTemplate\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDCACBC3-2038-41E3-9586-75AD71A91991}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA25F38B-4F8F-404A-8CE7-688613072CCB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -543,7 +543,7 @@
         <v>19</v>
       </c>
       <c r="C8">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="D8" t="s">
         <v>20</v>

--- a/MiniTemplate/Datas/random.xlsx
+++ b/MiniTemplate/Datas/random.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity Project\TimeChip\TimeChip\MiniTemplate\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA25F38B-4F8F-404A-8CE7-688613072CCB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A1A35C7-8FCF-40D4-8DA2-F32870EF50E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2205" yWindow="2265" windowWidth="20385" windowHeight="11235" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="27">
   <si>
     <t>##var</t>
   </si>
@@ -95,6 +95,12 @@
   </si>
   <si>
     <t>每月生成随机社区委托的概率</t>
+  </si>
+  <si>
+    <t>ConvenienceStore.SuperMarket.Spawn</t>
+  </si>
+  <si>
+    <t>每回合进入便利店触发超市找物小游戏的概率</t>
   </si>
 </sst>
 </file>
@@ -441,7 +447,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="2" max="2" width="39.375" customWidth="1"/>
@@ -571,6 +577,17 @@
         <v>24</v>
       </c>
     </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="B11" t="s">
+        <v>25</v>
+      </c>
+      <c r="C11">
+        <v>1</v>
+      </c>
+      <c r="D11" t="s">
+        <v>26</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/MiniTemplate/Datas/random.xlsx
+++ b/MiniTemplate/Datas/random.xlsx
@@ -1,131 +1,40 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity Project\TimeChip\TimeChip\MiniTemplate\Datas\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A1A35C7-8FCF-40D4-8DA2-F32870EF50E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2205" yWindow="2265" windowWidth="20385" windowHeight="11235" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="2205" yWindow="2265" windowWidth="20385" windowHeight="11235" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="27">
-  <si>
-    <t>##var</t>
-  </si>
-  <si>
-    <t>id</t>
-  </si>
-  <si>
-    <t>probability</t>
-  </si>
-  <si>
-    <t>desc</t>
-  </si>
-  <si>
-    <t>##type</t>
-  </si>
-  <si>
-    <t>string</t>
-  </si>
-  <si>
-    <t>float</t>
-  </si>
-  <si>
-    <t>##group</t>
-  </si>
-  <si>
-    <t>c,s</t>
-  </si>
-  <si>
-    <t>##comment</t>
-  </si>
-  <si>
-    <t>概率配置唯一键</t>
-  </si>
-  <si>
-    <t>触发概率（0-1）</t>
-  </si>
-  <si>
-    <t>说明</t>
-  </si>
-  <si>
-    <t>Community.TrashCan.Spawn</t>
-  </si>
-  <si>
-    <t>每个垃圾桶点位刷新的概率</t>
-  </si>
-  <si>
-    <t>Community.LostWallet.Spawn</t>
-  </si>
-  <si>
-    <t>遗失钱包出现概率</t>
-  </si>
-  <si>
-    <t>Community.StrayCatFoodBowl.Spawn</t>
-  </si>
-  <si>
-    <t>流浪猫食物盆出现概率</t>
-  </si>
-  <si>
-    <t>Community.Donation.Spawn</t>
-  </si>
-  <si>
-    <t>社区募捐箱出现概率</t>
-  </si>
-  <si>
-    <t>Clinic.Examination.RestoresHealth</t>
-  </si>
-  <si>
-    <t>体检恢复健康而非获得BUFF的概率</t>
-  </si>
-  <si>
-    <t>Mission.MonthlyOffer.Spawn</t>
-  </si>
-  <si>
-    <t>每月生成随机社区委托的概率</t>
-  </si>
-  <si>
-    <t>ConvenienceStore.SuperMarket.Spawn</t>
-  </si>
-  <si>
-    <t>每回合进入便利店触发超市找物小游戏的概率</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="2">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="宋体"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <family val="3"/>
       <sz val="9"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -144,21 +53,80 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -446,150 +414,228 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D11"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
-    <col min="2" max="2" width="39.375" customWidth="1"/>
-    <col min="3" max="3" width="16.75" customWidth="1"/>
-    <col min="4" max="4" width="31" customWidth="1"/>
+    <col width="39.375" customWidth="1" min="2" max="2"/>
+    <col width="16.75" customWidth="1" min="3" max="3"/>
+    <col width="31" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.15">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.15">
-      <c r="A2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.15">
-      <c r="A3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.15">
-      <c r="A4" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.15">
-      <c r="B5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C5">
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>##var</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>probability</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>desc</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>##type</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>##group</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>##comment</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>概率配置唯一键</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>触发概率（0-1）</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>说明</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Community.TrashCan.Spawn</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
         <v>0.1</v>
       </c>
-      <c r="D5" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.15">
-      <c r="B6" t="s">
-        <v>15</v>
-      </c>
-      <c r="C6">
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>每个垃圾桶点位刷新的概率</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Community.LostWallet.Spawn</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
         <v>0.1</v>
       </c>
-      <c r="D6" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.15">
-      <c r="B7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C7">
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>遗失钱包出现概率</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Community.StrayCatFoodBowl.Spawn</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
         <v>0.1</v>
       </c>
-      <c r="D7" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.15">
-      <c r="B8" t="s">
-        <v>19</v>
-      </c>
-      <c r="C8">
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>流浪猫食物盆出现概率</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Community.Donation.Spawn</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
         <v>0.3</v>
       </c>
-      <c r="D8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.15">
-      <c r="B9" t="s">
-        <v>21</v>
-      </c>
-      <c r="C9">
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>社区募捐箱出现概率</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Clinic.Examination.RestoresHealth</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
         <v>0.6</v>
       </c>
-      <c r="D9" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.15">
-      <c r="B10" t="s">
-        <v>23</v>
-      </c>
-      <c r="C10">
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>体检恢复健康而非获得BUFF的概率</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Mission.MonthlyOffer.Spawn</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
         <v>0.3</v>
       </c>
-      <c r="D10" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.15">
-      <c r="B11" t="s">
-        <v>25</v>
-      </c>
-      <c r="C11">
-        <v>1</v>
-      </c>
-      <c r="D11" t="s">
-        <v>26</v>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>每月生成随机社区委托的概率</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>ConvenienceStore.SuperMarket.Spawn</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>每回合进入便利店触发狐小满打折活动（超市找物小游戏）的概率</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Community.Centre.Submit.PrimaryGiftBox</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>社区中心提交材料获得初级社区物资礼盒的概率</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/MiniTemplate/Datas/random.xlsx
+++ b/MiniTemplate/Datas/random.xlsx
@@ -631,7 +631,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>社区中心提交材料获得初级社区物资礼盒的概率</t>
+          <t>社区中心每次提交材料时独立判定获得初级社区物资礼盒的概率</t>
         </is>
       </c>
     </row>

--- a/MiniTemplate/Datas/random.xlsx
+++ b/MiniTemplate/Datas/random.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="39.375" customWidth="1" min="2" max="2"/>
@@ -635,6 +635,21 @@
         </is>
       </c>
     </row>
+    <row r="13">
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Lottery.Normal.GrandPrize</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>普通奖池单次抽奖获得大奖的概率</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
